--- a/surveyWCgroup.xlsx
+++ b/surveyWCgroup.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ARG BALERDI - 2</t>
+          <t>ARG SENESI - 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -13333,7 +13333,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AUT BAUMGARTNER - 19</t>
+          <t>AUT LJUBICIC - 19</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BIH CELIK - 24</t>
+          <t>BIH MALIC - 24</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>BRA VINÍCIUS - 2</t>
+          <t>BRA EDERSON - 2</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -14695,11 +14695,6 @@
           <t>BRA3</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>BRA MAGALHAES - 3</t>
-        </is>
-      </c>
       <c r="D160" t="inlineStr">
         <is>
           <t>BRA</t>
@@ -16347,7 +16342,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>CAN FLORES - 26</t>
+          <t>CAN NELSON - 26</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -21187,7 +21182,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>ENG LIVRAMENTO - 12</t>
+          <t>ENG CHALOBAH - 12</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -22617,7 +22612,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>DEU KARL - 25</t>
+          <t>DEU OUEDRAOGO - 25</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -23519,7 +23514,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>HTI PIERRE - 14</t>
+          <t>HTI METUSALA - 14</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -24685,7 +24680,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>IRQ YAHYA - 15</t>
+          <t>IRQ MAKNZI - 15</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -25059,7 +25054,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>JPN ENDO - 6</t>
+          <t>JPN MACHINO - 6</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -25895,7 +25890,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>JOR SABRA - 18</t>
+          <t>JOR TAHA - 18</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -27325,7 +27320,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>MAR AGUERD - 5</t>
+          <t>MAR SAADANE - 5</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
@@ -27589,7 +27584,7 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>MAR EZZALZOULI - 17</t>
+          <t>MAR SBAI - 17</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
@@ -27831,7 +27826,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>NLD TIMBER - 2</t>
+          <t>NLD GEERTRUIDA - 2</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
@@ -28513,7 +28508,7 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>NZL GARBETT - 7</t>
+          <t>NZL ROGERSON - 7</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
